--- a/src/content/content_TEMPLATE.xlsx
+++ b/src/content/content_TEMPLATE.xlsx
@@ -8,409 +8,290 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eugsinsh gmail drive\NA\na_mi_pmu\src\content\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_6F02141B1187CD2440A29C219C96B5F510218368" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6401554-C1CB-4BDC-A11A-F32DD51AAC4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="ℹ️ Типы элементов" sheetId="1" r:id="rId1"/>
-    <sheet name="Шаблон заполнения" sheetId="2" r:id="rId2"/>
+    <sheet name="Шаблон заполнения" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="128">
-  <si>
-    <t>ТИП</t>
-  </si>
-  <si>
-    <t>ЧТО ЭТО?</t>
-  </si>
-  <si>
-    <t>РАЗМЕР</t>
-  </si>
-  <si>
-    <t>ГРАДИЕНТ</t>
-  </si>
-  <si>
-    <t>ИСПОЛЬЗОВАНИЕ</t>
-  </si>
-  <si>
-    <t>ПРИМЕР</t>
-  </si>
-  <si>
-    <t>НАЛОЖЕНИЕ</t>
-  </si>
-  <si>
-    <t>ВЫСОТА ГРАДИЕНТА</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="97">
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>type</t>
+  </si>
+  <si>
+    <t>ru</t>
+  </si>
+  <si>
+    <t>ua</t>
+  </si>
+  <si>
+    <t>gifRU</t>
+  </si>
+  <si>
+    <t>gifUA</t>
+  </si>
+  <si>
+    <t>imageRU</t>
+  </si>
+  <si>
+    <t>imageUA</t>
+  </si>
+  <si>
+    <t>titleRU</t>
+  </si>
+  <si>
+    <t>titleUA</t>
+  </si>
+  <si>
+    <t>descriptionRU</t>
+  </si>
+  <si>
+    <t>descriptionUA</t>
+  </si>
+  <si>
+    <t>href</t>
+  </si>
+  <si>
+    <t>imageWidth</t>
+  </si>
+  <si>
+    <t>imageHeight</t>
+  </si>
+  <si>
+    <t>imageAspectRatio</t>
+  </si>
+  <si>
+    <t>imageResizeMode</t>
+  </si>
+  <si>
+    <t>heroImage</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>images/hero.jpg</t>
+  </si>
+  <si>
+    <t>↑ Большой баннер вверху (100% ширина × 250px)</t>
+  </si>
+  <si>
+    <t>↑ Великий банер вверху (100% ширина × 250px)</t>
   </si>
   <si>
     <t>eyebrow</t>
   </si>
   <si>
-    <t>Маленький текст над заголовком - как подчеркивание или метка</t>
-  </si>
-  <si>
-    <t>12px, красный (#d84545), в верхнем регистре</t>
-  </si>
-  <si>
-    <t>Нет</t>
-  </si>
-  <si>
-    <t>Перед заголовком для визуального ударения или категории</t>
-  </si>
-  <si>
-    <t>BEAUTY ACADEMY, LESSON 1, NEW SECTION и т.д.</t>
-  </si>
-  <si>
-    <t>heroImage</t>
-  </si>
-  <si>
-    <t>Баннер/картинка вверху страницы с градиентным переходом в фон</t>
-  </si>
-  <si>
-    <t>100% ширина × 400px высота</t>
-  </si>
-  <si>
-    <t>Прозрачный → персиковый (#fff3eb)</t>
-  </si>
-  <si>
-    <t>Первый элемент на странице для визуального оформления</t>
-  </si>
-  <si>
-    <t>Следующий текст/контент заходит на картинку на 50px</t>
+    <t>Beauty Academy</t>
+  </si>
+  <si>
+    <t>title</t>
+  </si>
+  <si>
+    <t>Master the Art of Beauty</t>
+  </si>
+  <si>
+    <t>Оволодіти мистецтвом краси</t>
+  </si>
+  <si>
+    <t>subtitle</t>
+  </si>
+  <si>
+    <t>Основные направления обучения</t>
+  </si>
+  <si>
+    <t>Основні напрями навчання</t>
+  </si>
+  <si>
+    <t>text</t>
+  </si>
+  <si>
+    <t>Добро пожаловать на наш интерактивный курс. Здесь вы найдёте все необходимые знания и практические навыки для профессионального развития.</t>
+  </si>
+  <si>
+    <t>Ласкаво просимо на наш інтерактивний курс. Тут ви знайдете всі необхідні знання та практичні навички для професійного розвитку.</t>
   </si>
   <si>
     <t>squareImage</t>
   </si>
   <si>
-    <t>Квадратное изображение в центре контента</t>
-  </si>
-  <si>
-    <t>300×300px, по центру</t>
-  </si>
-  <si>
-    <t>Для демонстрации фото, схем, диаграмм</t>
-  </si>
-  <si>
-    <t>-</t>
+    <t>images/example_ru.jpg</t>
+  </si>
+  <si>
+    <t>images/example_ua.jpg</t>
+  </si>
+  <si>
+    <t>↑ Квадратное изображение (300×300px, по центру)</t>
+  </si>
+  <si>
+    <t>↑ Квадратне зображення (300×300px, по центру)</t>
+  </si>
+  <si>
+    <t>contain</t>
   </si>
   <si>
     <t>card</t>
   </si>
   <si>
-    <t>Карточка с изображением, заголовком и описанием</t>
-  </si>
-  <si>
-    <t>Полная ширина с обтеканием текста</t>
-  </si>
-  <si>
-    <t>Для ссылок на другие уроки/странички</t>
+    <t>images/card_ru.jpg</t>
+  </si>
+  <si>
+    <t>images/card_ua.jpg</t>
+  </si>
+  <si>
+    <t>Обычная карточка</t>
+  </si>
+  <si>
+    <t>Звичайна карточка</t>
+  </si>
+  <si>
+    <t>Описание - используется для ссылок на другие уроки</t>
+  </si>
+  <si>
+    <t>Опис - використовується для посилань на інші уроки</t>
+  </si>
+  <si>
+    <t>/other-page</t>
   </si>
   <si>
     <t>cardBig</t>
   </si>
   <si>
-    <t>Большая карточка - полноразмерная</t>
-  </si>
-  <si>
-    <t>280px ширина, картинка 100px, контент 150px</t>
-  </si>
-  <si>
-    <t>Для основных блоков с большим акцентом</t>
+    <t>images/lesson_big.jpg</t>
+  </si>
+  <si>
+    <t>Большая карточка (CardBig)</t>
+  </si>
+  <si>
+    <t>Велика карточка (CardBig)</t>
+  </si>
+  <si>
+    <t>Размер: 280px ширина, больший акцент</t>
+  </si>
+  <si>
+    <t>Розмір: 280px ширина, більший акцент</t>
+  </si>
+  <si>
+    <t>/lesson</t>
   </si>
   <si>
     <t>cardSmall</t>
   </si>
   <si>
-    <t>Малая карточка - компактная</t>
-  </si>
-  <si>
-    <t>160px ширина, картинка 80px, контент 100px</t>
-  </si>
-  <si>
-    <t>Для сетки или списков компактных элементов</t>
+    <t>images/test1.jpg</t>
+  </si>
+  <si>
+    <t>Малая карточка</t>
+  </si>
+  <si>
+    <t>Мала карточка</t>
+  </si>
+  <si>
+    <t>Размер: 160px, для списков</t>
+  </si>
+  <si>
+    <t>Розмір: 160px, для списків</t>
+  </si>
+  <si>
+    <t>/test</t>
+  </si>
+  <si>
+    <t>images/test2.jpg</t>
+  </si>
+  <si>
+    <t>Малая карточка 2</t>
+  </si>
+  <si>
+    <t>Мала карточка 2</t>
+  </si>
+  <si>
+    <t>Можно ставить несколько подряд</t>
+  </si>
+  <si>
+    <t>Можна ставити кілька поспіль</t>
+  </si>
+  <si>
+    <t>/test2</t>
+  </si>
+  <si>
+    <t>languageSwitcher</t>
+  </si>
+  <si>
+    <t>↑ Переключатель языка (Укр/Рус)</t>
+  </si>
+  <si>
+    <t>↑ Перемикач мови (Укр/Рус)</t>
+  </si>
+  <si>
+    <t>Что вы будете изучать:</t>
+  </si>
+  <si>
+    <t>Що ви будете вивчати:</t>
+  </si>
+  <si>
+    <t>item</t>
+  </si>
+  <si>
+    <t>Основные техники макияжа и подготовка кожи</t>
+  </si>
+  <si>
+    <t>Основні техніки макіяжу та підготовка шкіри</t>
+  </si>
+  <si>
+    <t>Цветовая теория и подбор оттенков</t>
+  </si>
+  <si>
+    <t>Теорія кольору та підбір відтінків</t>
+  </si>
+  <si>
+    <t>Работа с различными типами кожи</t>
+  </si>
+  <si>
+    <t>Робота з різними типами шкіри</t>
+  </si>
+  <si>
+    <t>Вы получите практический опыт и сертификат после прохождения курса.</t>
+  </si>
+  <si>
+    <t>Ви отримаєте практичний досвід та сертифікат після проходження курсу.</t>
+  </si>
+  <si>
+    <t>textLink</t>
+  </si>
+  <si>
+    <t>Узнать больше о программе обучения →</t>
+  </si>
+  <si>
+    <t>Дізнатися більше про програму навчання →</t>
+  </si>
+  <si>
+    <t>/learn-more</t>
+  </si>
+  <si>
+    <t>videoContainer</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/embed/dQw4w9WgXcQ</t>
+  </si>
+  <si>
+    <t>↑ Видеоэлемент (указать URL видео на YouTube)</t>
+  </si>
+  <si>
+    <t>↑ Відеоелемент (вказати URL відео на YouTube)</t>
   </si>
   <si>
     <t>gif</t>
   </si>
   <si>
-    <t>Анимированное GIF-изображение</t>
-  </si>
-  <si>
-    <t>Рекомендуется 300–600px ширина</t>
-  </si>
-  <si>
-    <t>Визуальный акцент, демонстрация движения</t>
-  </si>
-  <si>
-    <t>Укажите путь в gifRU / gifUA, например images/animation_ru.gif</t>
-  </si>
-  <si>
-    <t>id</t>
-  </si>
-  <si>
-    <t>type</t>
-  </si>
-  <si>
-    <t>ru</t>
-  </si>
-  <si>
-    <t>ua</t>
-  </si>
-  <si>
-    <t>gifRU</t>
-  </si>
-  <si>
-    <t>gifUA</t>
-  </si>
-  <si>
-    <t>imageRU</t>
-  </si>
-  <si>
-    <t>imageUA</t>
-  </si>
-  <si>
-    <t>titleRU</t>
-  </si>
-  <si>
-    <t>titleUA</t>
-  </si>
-  <si>
-    <t>descriptionRU</t>
-  </si>
-  <si>
-    <t>descriptionUA</t>
-  </si>
-  <si>
-    <t>href</t>
-  </si>
-  <si>
-    <t>imageWidth</t>
-  </si>
-  <si>
-    <t>imageHeight</t>
-  </si>
-  <si>
-    <t>imageAspectRatio</t>
-  </si>
-  <si>
-    <t>imageResizeMode</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>images/hero.jpg</t>
-  </si>
-  <si>
-    <t>↑ Большой баннер вверху (100% ширина × 250px)</t>
-  </si>
-  <si>
-    <t>↑ Великий банер вверху (100% ширина × 250px)</t>
-  </si>
-  <si>
-    <t>Beauty Academy</t>
-  </si>
-  <si>
-    <t>title</t>
-  </si>
-  <si>
-    <t>Master the Art of Beauty</t>
-  </si>
-  <si>
-    <t>Оволодіти мистецтвом краси</t>
-  </si>
-  <si>
-    <t>subtitle</t>
-  </si>
-  <si>
-    <t>Основные направления обучения</t>
-  </si>
-  <si>
-    <t>Основні напрями навчання</t>
-  </si>
-  <si>
-    <t>text</t>
-  </si>
-  <si>
-    <t>Добро пожаловать на наш интерактивный курс. Здесь вы найдёте все необходимые знания и практические навыки для профессионального развития.</t>
-  </si>
-  <si>
-    <t>Ласкаво просимо на наш інтерактивний курс. Тут ви знайдете всі необхідні знання та практичні навички для професійного розвитку.</t>
-  </si>
-  <si>
-    <t>images/example_ru.jpg</t>
-  </si>
-  <si>
-    <t>images/example_ua.jpg</t>
-  </si>
-  <si>
-    <t>↑ Квадратное изображение (300×300px, по центру)</t>
-  </si>
-  <si>
-    <t>↑ Квадратне зображення (300×300px, по центру)</t>
-  </si>
-  <si>
-    <t>contain</t>
-  </si>
-  <si>
-    <t>images/card_ru.jpg</t>
-  </si>
-  <si>
-    <t>images/card_ua.jpg</t>
-  </si>
-  <si>
-    <t>Обычная карточка</t>
-  </si>
-  <si>
-    <t>Звичайна карточка</t>
-  </si>
-  <si>
-    <t>Описание - используется для ссылок на другие уроки</t>
-  </si>
-  <si>
-    <t>Опис - використовується для посилань на інші уроки</t>
-  </si>
-  <si>
-    <t>/other-page</t>
-  </si>
-  <si>
-    <t>images/lesson_big.jpg</t>
-  </si>
-  <si>
-    <t>Большая карточка (CardBig)</t>
-  </si>
-  <si>
-    <t>Велика карточка (CardBig)</t>
-  </si>
-  <si>
-    <t>Размер: 280px ширина, больший акцент</t>
-  </si>
-  <si>
-    <t>Розмір: 280px ширина, більший акцент</t>
-  </si>
-  <si>
-    <t>/lesson</t>
-  </si>
-  <si>
-    <t>images/test1.jpg</t>
-  </si>
-  <si>
-    <t>Малая карточка</t>
-  </si>
-  <si>
-    <t>Мала карточка</t>
-  </si>
-  <si>
-    <t>Размер: 160px, для списков</t>
-  </si>
-  <si>
-    <t>Розмір: 160px, для списків</t>
-  </si>
-  <si>
-    <t>/test</t>
-  </si>
-  <si>
-    <t>images/test2.jpg</t>
-  </si>
-  <si>
-    <t>Малая карточка 2</t>
-  </si>
-  <si>
-    <t>Мала карточка 2</t>
-  </si>
-  <si>
-    <t>Можно ставить несколько подряд</t>
-  </si>
-  <si>
-    <t>Можна ставити кілька поспіль</t>
-  </si>
-  <si>
-    <t>/test2</t>
-  </si>
-  <si>
-    <t>languageSwitcher</t>
-  </si>
-  <si>
-    <t>↑ Переключатель языка (Укр/Рус)</t>
-  </si>
-  <si>
-    <t>↑ Перемикач мови (Укр/Рус)</t>
-  </si>
-  <si>
-    <t>Что вы будете изучать:</t>
-  </si>
-  <si>
-    <t>Що ви будете вивчати:</t>
-  </si>
-  <si>
-    <t>item</t>
-  </si>
-  <si>
-    <t>Основные техники макияжа и подготовка кожи</t>
-  </si>
-  <si>
-    <t>Основні техніки макіяжу та підготовка шкіри</t>
-  </si>
-  <si>
-    <t>Цветовая теория и подбор оттенков</t>
-  </si>
-  <si>
-    <t>Теорія кольору та підбір відтінків</t>
-  </si>
-  <si>
-    <t>Работа с различными типами кожи</t>
-  </si>
-  <si>
-    <t>Робота з різними типами шкіри</t>
-  </si>
-  <si>
-    <t>Вы получите практический опыт и сертификат после прохождения курса.</t>
-  </si>
-  <si>
-    <t>Ви отримаєте практичний досвід та сертифікат після проходження курсу.</t>
-  </si>
-  <si>
-    <t>textLink</t>
-  </si>
-  <si>
-    <t>Узнать больше о программе обучения →</t>
-  </si>
-  <si>
-    <t>Дізнатися більше про програму навчання →</t>
-  </si>
-  <si>
-    <t>/learn-more</t>
-  </si>
-  <si>
-    <t>videoContainer</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/embed/dQw4w9WgXcQ</t>
-  </si>
-  <si>
-    <t>↑ Видеоэлемент (указать URL видео на YouTube)</t>
-  </si>
-  <si>
-    <t>↑ Відеоелемент (вказати URL відео на YouTube)</t>
-  </si>
-  <si>
     <t>images/animation_ru.gif</t>
   </si>
   <si>
@@ -418,6 +299,18 @@
   </si>
   <si>
     <t>16:9</t>
+  </si>
+  <si>
+    <t>navigationButtons</t>
+  </si>
+  <si>
+    <t>Следующий урок</t>
+  </si>
+  <si>
+    <t>Наступний урок</t>
+  </si>
+  <si>
+    <t>/pigment</t>
   </si>
 </sst>
 </file>
@@ -794,194 +687,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="20.875" customWidth="1"/>
-    <col min="2" max="2" width="40.875" customWidth="1"/>
-    <col min="3" max="3" width="30.875" customWidth="1"/>
-    <col min="4" max="4" width="25.875" customWidth="1"/>
-    <col min="5" max="5" width="40.875" customWidth="1"/>
-    <col min="6" max="6" width="20.875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" t="s">
-        <v>23</v>
-      </c>
-      <c r="H4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>25</v>
-      </c>
-      <c r="B5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" t="s">
-        <v>28</v>
-      </c>
-      <c r="H5" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>29</v>
-      </c>
-      <c r="B6" t="s">
-        <v>30</v>
-      </c>
-      <c r="C6" t="s">
-        <v>31</v>
-      </c>
-      <c r="D6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E6" t="s">
-        <v>32</v>
-      </c>
-      <c r="H6" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>33</v>
-      </c>
-      <c r="B7" t="s">
-        <v>34</v>
-      </c>
-      <c r="C7" t="s">
-        <v>35</v>
-      </c>
-      <c r="D7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E7" t="s">
-        <v>36</v>
-      </c>
-      <c r="H7" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>37</v>
-      </c>
-      <c r="B8" t="s">
-        <v>38</v>
-      </c>
-      <c r="C8" t="s">
-        <v>39</v>
-      </c>
-      <c r="D8" t="s">
-        <v>11</v>
-      </c>
-      <c r="E8" t="s">
-        <v>40</v>
-      </c>
-      <c r="F8" t="s">
-        <v>41</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <ignoredErrors>
-    <ignoredError sqref="A1:H8" numberStoredAsText="1"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:Q20"/>
+  <dimension ref="A1:Q21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.875" customWidth="1"/>
@@ -997,55 +703,55 @@
   <sheetData>
     <row r="1" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>43</v>
+        <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>44</v>
+        <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>45</v>
+        <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>46</v>
+        <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="G1" t="s">
-        <v>48</v>
+        <v>6</v>
       </c>
       <c r="H1" t="s">
-        <v>49</v>
+        <v>7</v>
       </c>
       <c r="I1" t="s">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="J1" t="s">
-        <v>51</v>
+        <v>9</v>
       </c>
       <c r="K1" t="s">
-        <v>52</v>
+        <v>10</v>
       </c>
       <c r="L1" t="s">
-        <v>53</v>
+        <v>11</v>
       </c>
       <c r="M1" t="s">
-        <v>54</v>
+        <v>12</v>
       </c>
       <c r="N1" t="s">
-        <v>55</v>
+        <v>13</v>
       </c>
       <c r="O1" t="s">
-        <v>56</v>
+        <v>14</v>
       </c>
       <c r="P1" t="s">
-        <v>57</v>
+        <v>15</v>
       </c>
       <c r="Q1" t="s">
-        <v>58</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
@@ -1053,52 +759,52 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C2" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="D2" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="E2" t="s">
-        <v>60</v>
+        <v>19</v>
       </c>
       <c r="F2" t="s">
-        <v>60</v>
+        <v>19</v>
       </c>
       <c r="G2" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="H2" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="I2" t="s">
-        <v>61</v>
+        <v>20</v>
       </c>
       <c r="J2" t="s">
-        <v>62</v>
+        <v>21</v>
       </c>
       <c r="K2" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="L2" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="M2" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="N2" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="O2" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="P2" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="Q2" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
@@ -1106,52 +812,52 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>63</v>
+        <v>23</v>
       </c>
       <c r="D3" t="s">
-        <v>63</v>
+        <v>23</v>
       </c>
       <c r="E3" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="F3" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="G3" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="H3" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="I3" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="J3" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="K3" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="L3" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="M3" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="N3" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="O3" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="P3" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="Q3" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
@@ -1159,52 +865,52 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>64</v>
+        <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>65</v>
+        <v>25</v>
       </c>
       <c r="D4" t="s">
-        <v>66</v>
+        <v>26</v>
       </c>
       <c r="E4" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="F4" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="G4" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="H4" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="I4" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="J4" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="K4" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="L4" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="M4" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="N4" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="O4" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="P4" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="Q4" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
@@ -1212,52 +918,52 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>67</v>
+        <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>68</v>
+        <v>28</v>
       </c>
       <c r="D5" t="s">
-        <v>69</v>
+        <v>29</v>
       </c>
       <c r="E5" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="F5" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="G5" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="H5" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="I5" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="J5" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="K5" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="L5" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="M5" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="N5" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="O5" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="P5" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="Q5" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
@@ -1265,52 +971,52 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="C6" t="s">
-        <v>71</v>
+        <v>31</v>
       </c>
       <c r="D6" t="s">
-        <v>72</v>
+        <v>32</v>
       </c>
       <c r="E6" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="F6" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="G6" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="H6" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="I6" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="J6" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="K6" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="L6" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="M6" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="N6" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="O6" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="P6" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="Q6" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
@@ -1318,34 +1024,34 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="C7" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="D7" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="E7" t="s">
-        <v>73</v>
+        <v>34</v>
       </c>
       <c r="F7" t="s">
-        <v>74</v>
+        <v>35</v>
       </c>
       <c r="G7" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="H7" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="I7" t="s">
-        <v>75</v>
+        <v>36</v>
       </c>
       <c r="J7" t="s">
-        <v>76</v>
+        <v>37</v>
       </c>
       <c r="K7" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="L7">
         <v>300</v>
@@ -1357,13 +1063,13 @@
         <v>1</v>
       </c>
       <c r="O7" t="s">
-        <v>77</v>
+        <v>38</v>
       </c>
       <c r="P7" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="Q7" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
@@ -1371,52 +1077,52 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="C8" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="D8" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="E8" t="s">
-        <v>78</v>
+        <v>40</v>
       </c>
       <c r="F8" t="s">
-        <v>79</v>
+        <v>41</v>
       </c>
       <c r="G8" t="s">
-        <v>80</v>
+        <v>42</v>
       </c>
       <c r="H8" t="s">
-        <v>81</v>
+        <v>43</v>
       </c>
       <c r="I8" t="s">
-        <v>82</v>
+        <v>44</v>
       </c>
       <c r="J8" t="s">
-        <v>83</v>
+        <v>45</v>
       </c>
       <c r="K8" t="s">
-        <v>84</v>
+        <v>46</v>
       </c>
       <c r="L8" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="M8" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="N8" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="O8" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="P8" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="Q8" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
@@ -1424,52 +1130,52 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="C9" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="D9" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="E9" t="s">
-        <v>85</v>
+        <v>48</v>
       </c>
       <c r="F9" t="s">
-        <v>85</v>
+        <v>48</v>
       </c>
       <c r="G9" t="s">
-        <v>86</v>
+        <v>49</v>
       </c>
       <c r="H9" t="s">
-        <v>87</v>
+        <v>50</v>
       </c>
       <c r="I9" t="s">
-        <v>88</v>
+        <v>51</v>
       </c>
       <c r="J9" t="s">
-        <v>89</v>
+        <v>52</v>
       </c>
       <c r="K9" t="s">
-        <v>90</v>
+        <v>53</v>
       </c>
       <c r="L9" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="M9" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="N9" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="O9" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="P9" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="Q9" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
@@ -1477,52 +1183,52 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="C10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" t="s">
+        <v>55</v>
+      </c>
+      <c r="F10" t="s">
+        <v>55</v>
+      </c>
+      <c r="G10" t="s">
+        <v>56</v>
+      </c>
+      <c r="H10" t="s">
+        <v>57</v>
+      </c>
+      <c r="I10" t="s">
+        <v>58</v>
+      </c>
+      <c r="J10" t="s">
         <v>59</v>
       </c>
-      <c r="D10" t="s">
-        <v>59</v>
-      </c>
-      <c r="E10" t="s">
-        <v>91</v>
-      </c>
-      <c r="F10" t="s">
-        <v>91</v>
-      </c>
-      <c r="G10" t="s">
-        <v>92</v>
-      </c>
-      <c r="H10" t="s">
-        <v>93</v>
-      </c>
-      <c r="I10" t="s">
-        <v>94</v>
-      </c>
-      <c r="J10" t="s">
-        <v>95</v>
-      </c>
       <c r="K10" t="s">
-        <v>96</v>
+        <v>60</v>
       </c>
       <c r="L10" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="M10" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="N10" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="O10" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="P10" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="Q10" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
@@ -1530,52 +1236,52 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="C11" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="D11" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="E11" t="s">
-        <v>97</v>
+        <v>61</v>
       </c>
       <c r="F11" t="s">
-        <v>97</v>
+        <v>61</v>
       </c>
       <c r="G11" t="s">
-        <v>98</v>
+        <v>62</v>
       </c>
       <c r="H11" t="s">
-        <v>99</v>
+        <v>63</v>
       </c>
       <c r="I11" t="s">
-        <v>100</v>
+        <v>64</v>
       </c>
       <c r="J11" t="s">
-        <v>101</v>
+        <v>65</v>
       </c>
       <c r="K11" t="s">
-        <v>102</v>
+        <v>66</v>
       </c>
       <c r="L11" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="M11" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="N11" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="O11" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="P11" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="Q11" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
@@ -1583,52 +1289,52 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>103</v>
+        <v>67</v>
       </c>
       <c r="C12" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="D12" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="E12" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="F12" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="G12" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="H12" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="I12" t="s">
-        <v>104</v>
+        <v>68</v>
       </c>
       <c r="J12" t="s">
-        <v>105</v>
+        <v>69</v>
       </c>
       <c r="K12" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="L12" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="M12" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="N12" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="O12" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="P12" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="Q12" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
@@ -1636,52 +1342,52 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>67</v>
+        <v>27</v>
       </c>
       <c r="C13" t="s">
-        <v>106</v>
+        <v>70</v>
       </c>
       <c r="D13" t="s">
-        <v>107</v>
+        <v>71</v>
       </c>
       <c r="E13" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="F13" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="G13" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="H13" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="I13" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="J13" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="K13" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="L13" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="M13" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="N13" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="O13" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="P13" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="Q13" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
     </row>
     <row r="14" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
@@ -1689,52 +1395,52 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>108</v>
+        <v>72</v>
       </c>
       <c r="C14" t="s">
-        <v>109</v>
+        <v>73</v>
       </c>
       <c r="D14" t="s">
-        <v>110</v>
+        <v>74</v>
       </c>
       <c r="E14" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="F14" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="G14" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="H14" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="I14" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="J14" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="K14" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="L14" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="M14" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="N14" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="O14" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="P14" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="Q14" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
     </row>
     <row r="15" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
@@ -1742,52 +1448,52 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>108</v>
+        <v>72</v>
       </c>
       <c r="C15" t="s">
-        <v>111</v>
+        <v>75</v>
       </c>
       <c r="D15" t="s">
-        <v>112</v>
+        <v>76</v>
       </c>
       <c r="E15" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="F15" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="G15" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="H15" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="I15" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="J15" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="K15" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="L15" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="M15" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="N15" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="O15" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="P15" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="Q15" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
@@ -1795,52 +1501,52 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>108</v>
+        <v>72</v>
       </c>
       <c r="C16" t="s">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="D16" t="s">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="E16" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="F16" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="G16" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="H16" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="I16" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="J16" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="K16" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="L16" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="M16" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="N16" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="O16" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="P16" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="Q16" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
     </row>
     <row r="17" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
@@ -1848,52 +1554,52 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="C17" t="s">
-        <v>115</v>
+        <v>79</v>
       </c>
       <c r="D17" t="s">
-        <v>116</v>
+        <v>80</v>
       </c>
       <c r="E17" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="F17" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="G17" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="H17" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="I17" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="J17" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="K17" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="L17" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="M17" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="N17" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="O17" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="P17" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="Q17" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
     </row>
     <row r="18" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
@@ -1901,52 +1607,52 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="C18" t="s">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="D18" t="s">
-        <v>119</v>
+        <v>83</v>
       </c>
       <c r="E18" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="F18" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="G18" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="H18" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="I18" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="J18" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="K18" t="s">
-        <v>120</v>
+        <v>84</v>
       </c>
       <c r="L18" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="M18" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="N18" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="O18" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="P18" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="Q18" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
@@ -1954,52 +1660,52 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>121</v>
+        <v>85</v>
       </c>
       <c r="C19" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="D19" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="E19" t="s">
-        <v>122</v>
+        <v>86</v>
       </c>
       <c r="F19" t="s">
-        <v>122</v>
+        <v>86</v>
       </c>
       <c r="G19" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="H19" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="I19" t="s">
-        <v>123</v>
+        <v>87</v>
       </c>
       <c r="J19" t="s">
-        <v>124</v>
+        <v>88</v>
       </c>
       <c r="K19" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="L19" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="M19" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="N19" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="O19" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="P19" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="Q19" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
     </row>
     <row r="20" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
@@ -2007,34 +1713,34 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>37</v>
+        <v>89</v>
       </c>
       <c r="C20" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="D20" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="E20" t="s">
-        <v>125</v>
+        <v>90</v>
       </c>
       <c r="F20" t="s">
-        <v>126</v>
+        <v>91</v>
       </c>
       <c r="G20" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="H20" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="I20" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="J20" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="K20" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="L20">
         <v>400</v>
@@ -2043,22 +1749,72 @@
         <v>225</v>
       </c>
       <c r="N20" t="s">
-        <v>127</v>
+        <v>92</v>
       </c>
       <c r="O20" t="s">
-        <v>77</v>
+        <v>38</v>
       </c>
       <c r="P20" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="Q20" t="s">
-        <v>59</v>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>93</v>
+      </c>
+      <c r="C21" t="s">
+        <v>94</v>
+      </c>
+      <c r="D21" t="s">
+        <v>95</v>
+      </c>
+      <c r="E21" t="s">
+        <v>18</v>
+      </c>
+      <c r="F21" t="s">
+        <v>18</v>
+      </c>
+      <c r="G21" t="s">
+        <v>18</v>
+      </c>
+      <c r="H21" t="s">
+        <v>18</v>
+      </c>
+      <c r="I21" t="s">
+        <v>18</v>
+      </c>
+      <c r="J21" t="s">
+        <v>18</v>
+      </c>
+      <c r="K21" t="s">
+        <v>18</v>
+      </c>
+      <c r="M21" t="s">
+        <v>96</v>
+      </c>
+      <c r="N21" t="s">
+        <v>18</v>
+      </c>
+      <c r="O21" t="s">
+        <v>18</v>
+      </c>
+      <c r="P21" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:Q20" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:Q20 A21:K21 N21:Q21" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/src/content/content_TEMPLATE.xlsx
+++ b/src/content/content_TEMPLATE.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:L14"/>
   <cols>
     <col min="1" max="1" width="5.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -609,31 +609,31 @@
         <v>5</v>
       </c>
       <c r="B6" t="str">
-        <v>text</v>
+        <v>languageSwitcher</v>
       </c>
       <c r="C6" t="str">
-        <v>Цей текст відображається як звичайний абзац.</v>
+        <v>UA</v>
       </c>
       <c r="D6" t="str">
-        <v>Этот текст выводится как обычный параграф.</v>
+        <v>RU</v>
       </c>
       <c r="E6" t="str">
-        <v>This text is rendered as a normal paragraph.</v>
+        <v>EN</v>
       </c>
       <c r="F6" t="str">
-        <v>Dieser Text wird als normaler Absatz angezeigt.</v>
+        <v>DE</v>
       </c>
       <c r="G6" t="str">
-        <v/>
+        <v>Переключатель языка</v>
       </c>
       <c r="H6" t="str">
-        <v/>
+        <v>Переключатель языка</v>
       </c>
       <c r="I6" t="str">
-        <v/>
+        <v>Language switcher</v>
       </c>
       <c r="J6" t="str">
-        <v/>
+        <v>Sprachumschalter</v>
       </c>
       <c r="K6" t="str">
         <v/>
@@ -647,19 +647,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="str">
-        <v>image</v>
+        <v>text</v>
       </c>
       <c r="C7" t="str">
-        <v>images/example.jpg</v>
+        <v>Цей текст відображається як звичайний абзац.</v>
       </c>
       <c r="D7" t="str">
-        <v>images/example.jpg</v>
+        <v>Этот текст выводится как обычный параграф.</v>
       </c>
       <c r="E7" t="str">
-        <v>images/example.jpg</v>
+        <v>This text is rendered as a normal paragraph.</v>
       </c>
       <c r="F7" t="str">
-        <v>images/example.jpg</v>
+        <v>Dieser Text wird als normaler Absatz angezeigt.</v>
       </c>
       <c r="G7" t="str">
         <v/>
@@ -677,27 +677,27 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>w=600;h=400;resizeMode=contain</v>
+        <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B8" t="str">
-        <v>gif</v>
+        <v>image</v>
       </c>
       <c r="C8" t="str">
-        <v>images/animation.gif</v>
+        <v>images/example.jpg</v>
       </c>
       <c r="D8" t="str">
-        <v>images/animation.gif</v>
+        <v>images/example.jpg</v>
       </c>
       <c r="E8" t="str">
-        <v>images/animation.gif</v>
+        <v>images/example.jpg</v>
       </c>
       <c r="F8" t="str">
-        <v>images/animation.gif</v>
+        <v>images/example.jpg</v>
       </c>
       <c r="G8" t="str">
         <v/>
@@ -715,80 +715,80 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>w=400;h=225;resizeMode=contain</v>
+        <v>w=600;h=400;resizeMode=contain</v>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B9" t="str">
-        <v>card</v>
+        <v>gif</v>
       </c>
       <c r="C9" t="str">
-        <v>Заголовок карточки</v>
+        <v>images/animation.gif</v>
       </c>
       <c r="D9" t="str">
-        <v>Заголовок карточки</v>
+        <v>images/animation.gif</v>
       </c>
       <c r="E9" t="str">
-        <v>Card title</v>
+        <v>images/animation.gif</v>
       </c>
       <c r="F9" t="str">
-        <v>Kartenüberschrift</v>
+        <v>images/animation.gif</v>
       </c>
       <c r="G9" t="str">
-        <v>Опис карточки українською</v>
+        <v/>
       </c>
       <c r="H9" t="str">
-        <v>Описание карточки на русском</v>
+        <v/>
       </c>
       <c r="I9" t="str">
-        <v>Card description in English</v>
+        <v/>
       </c>
       <c r="J9" t="str">
-        <v>Kartenbeschreibung auf Deutsch</v>
+        <v/>
       </c>
       <c r="K9" t="str">
-        <v>/lesson-example</v>
+        <v/>
       </c>
       <c r="L9" t="str">
-        <v/>
+        <v>w=400;h=225;resizeMode=contain</v>
       </c>
     </row>
     <row r="10">
       <c r="A10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B10" t="str">
-        <v>video</v>
+        <v>card</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=dQw4w9WgXcQ</v>
+        <v>Заголовок карточки</v>
       </c>
       <c r="D10" t="str">
-        <v>https://www.youtube.com/watch?v=dQw4w9WgXcQ</v>
+        <v>Заголовок карточки</v>
       </c>
       <c r="E10" t="str">
-        <v>https://www.youtube.com/watch?v=dQw4w9WgXcQ</v>
+        <v>Card title</v>
       </c>
       <c r="F10" t="str">
-        <v>https://www.youtube.com/watch?v=dQw4w9WgXcQ</v>
+        <v>Kartenüberschrift</v>
       </c>
       <c r="G10" t="str">
-        <v/>
+        <v>Опис карточки українською</v>
       </c>
       <c r="H10" t="str">
-        <v/>
+        <v>Описание карточки на русском</v>
       </c>
       <c r="I10" t="str">
-        <v/>
+        <v>Card description in English</v>
       </c>
       <c r="J10" t="str">
-        <v/>
+        <v>Kartenbeschreibung auf Deutsch</v>
       </c>
       <c r="K10" t="str">
-        <v/>
+        <v>/lesson-example</v>
       </c>
       <c r="L10" t="str">
         <v/>
@@ -796,22 +796,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B11" t="str">
-        <v>link</v>
+        <v>video</v>
       </c>
       <c r="C11" t="str">
-        <v>Детальніше про курс</v>
+        <v>https://www.youtube.com/watch?v=dQw4w9WgXcQ</v>
       </c>
       <c r="D11" t="str">
-        <v>Подробнее о курсе</v>
+        <v>https://www.youtube.com/watch?v=dQw4w9WgXcQ</v>
       </c>
       <c r="E11" t="str">
-        <v>Read more about the course</v>
+        <v>https://www.youtube.com/watch?v=dQw4w9WgXcQ</v>
       </c>
       <c r="F11" t="str">
-        <v>Mehr über den Kurs</v>
+        <v>https://www.youtube.com/watch?v=dQw4w9WgXcQ</v>
       </c>
       <c r="G11" t="str">
         <v/>
@@ -826,7 +826,7 @@
         <v/>
       </c>
       <c r="K11" t="str">
-        <v>/course</v>
+        <v/>
       </c>
       <c r="L11" t="str">
         <v/>
@@ -834,22 +834,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B12" t="str">
-        <v>item</v>
+        <v>link</v>
       </c>
       <c r="C12" t="str">
-        <v>Пункт списку UA</v>
+        <v>Детальніше про курс</v>
       </c>
       <c r="D12" t="str">
-        <v>Пункт списка RU</v>
+        <v>Подробнее о курсе</v>
       </c>
       <c r="E12" t="str">
-        <v>List item EN</v>
+        <v>Read more about the course</v>
       </c>
       <c r="F12" t="str">
-        <v>Listenelement DE</v>
+        <v>Mehr über den Kurs</v>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -864,7 +864,7 @@
         <v/>
       </c>
       <c r="K12" t="str">
-        <v/>
+        <v>/course</v>
       </c>
       <c r="L12" t="str">
         <v/>
@@ -872,45 +872,83 @@
     </row>
     <row r="13">
       <c r="A13">
+        <v>11</v>
+      </c>
+      <c r="B13" t="str">
+        <v>item</v>
+      </c>
+      <c r="C13" t="str">
+        <v>Пункт списку UA</v>
+      </c>
+      <c r="D13" t="str">
+        <v>Пункт списка RU</v>
+      </c>
+      <c r="E13" t="str">
+        <v>List item EN</v>
+      </c>
+      <c r="F13" t="str">
+        <v>Listenelement DE</v>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v/>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
+      <c r="K13" t="str">
+        <v/>
+      </c>
+      <c r="L13" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
         <v>12</v>
       </c>
-      <c r="B13" t="str">
+      <c r="B14" t="str">
         <v>navigationButtons</v>
       </c>
-      <c r="C13" t="str">
+      <c r="C14" t="str">
         <v>Наступний урок</v>
       </c>
-      <c r="D13" t="str">
+      <c r="D14" t="str">
         <v>Следующий урок</v>
       </c>
-      <c r="E13" t="str">
+      <c r="E14" t="str">
         <v>Next lesson</v>
       </c>
-      <c r="F13" t="str">
+      <c r="F14" t="str">
         <v>Nächste Lektion</v>
       </c>
-      <c r="G13" t="str">
-        <v/>
-      </c>
-      <c r="H13" t="str">
-        <v/>
-      </c>
-      <c r="I13" t="str">
-        <v/>
-      </c>
-      <c r="J13" t="str">
-        <v/>
-      </c>
-      <c r="K13" t="str">
+      <c r="G14" t="str">
+        <v/>
+      </c>
+      <c r="H14" t="str">
+        <v/>
+      </c>
+      <c r="I14" t="str">
+        <v/>
+      </c>
+      <c r="J14" t="str">
+        <v/>
+      </c>
+      <c r="K14" t="str">
         <v>/next-page</v>
       </c>
-      <c r="L13" t="str">
+      <c r="L14" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L13"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L14"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/src/content/content_TEMPLATE.xlsx
+++ b/src/content/content_TEMPLATE.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L17"/>
+  <dimension ref="A1:L18"/>
   <cols>
     <col min="1" max="1" width="5.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -1060,9 +1060,47 @@
         <v/>
       </c>
     </row>
+    <row r="18">
+      <c r="A18">
+        <v>16</v>
+      </c>
+      <c r="B18" t="str">
+        <v>timer</v>
+      </c>
+      <c r="C18" t="str">
+        <v/>
+      </c>
+      <c r="D18" t="str">
+        <v/>
+      </c>
+      <c r="E18" t="str">
+        <v/>
+      </c>
+      <c r="F18" t="str">
+        <v/>
+      </c>
+      <c r="G18" t="str">
+        <v/>
+      </c>
+      <c r="H18" t="str">
+        <v/>
+      </c>
+      <c r="I18" t="str">
+        <v/>
+      </c>
+      <c r="J18" t="str">
+        <v/>
+      </c>
+      <c r="K18" t="str">
+        <v/>
+      </c>
+      <c r="L18" t="str">
+        <v>seconds=180</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L17"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L18"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/src/content/content_TEMPLATE.xlsx
+++ b/src/content/content_TEMPLATE.xlsx
@@ -5,6 +5,7 @@
   <sheets>
     <sheet name="Шаблон заполнения" sheetId="1" r:id="rId1"/>
     <sheet name="quiz1" sheetId="2" r:id="rId2"/>
+    <sheet name="checklist1" sheetId="3" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
@@ -398,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L18"/>
+  <dimension ref="A1:L19"/>
   <cols>
     <col min="1" max="1" width="5.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -1065,42 +1066,80 @@
         <v>16</v>
       </c>
       <c r="B18" t="str">
+        <v>checklist</v>
+      </c>
+      <c r="C18" t="str">
+        <v>Список задач</v>
+      </c>
+      <c r="D18" t="str">
+        <v>Список задач</v>
+      </c>
+      <c r="E18" t="str">
+        <v>Checklist</v>
+      </c>
+      <c r="F18" t="str">
+        <v>Checkliste</v>
+      </c>
+      <c r="G18" t="str">
+        <v/>
+      </c>
+      <c r="H18" t="str">
+        <v/>
+      </c>
+      <c r="I18" t="str">
+        <v/>
+      </c>
+      <c r="J18" t="str">
+        <v/>
+      </c>
+      <c r="K18" t="str">
+        <v>checklist1</v>
+      </c>
+      <c r="L18" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>17</v>
+      </c>
+      <c r="B19" t="str">
         <v>timer</v>
       </c>
-      <c r="C18" t="str">
-        <v/>
-      </c>
-      <c r="D18" t="str">
-        <v/>
-      </c>
-      <c r="E18" t="str">
-        <v/>
-      </c>
-      <c r="F18" t="str">
-        <v/>
-      </c>
-      <c r="G18" t="str">
-        <v/>
-      </c>
-      <c r="H18" t="str">
-        <v/>
-      </c>
-      <c r="I18" t="str">
-        <v/>
-      </c>
-      <c r="J18" t="str">
-        <v/>
-      </c>
-      <c r="K18" t="str">
-        <v/>
-      </c>
-      <c r="L18" t="str">
+      <c r="C19" t="str">
+        <v/>
+      </c>
+      <c r="D19" t="str">
+        <v/>
+      </c>
+      <c r="E19" t="str">
+        <v/>
+      </c>
+      <c r="F19" t="str">
+        <v/>
+      </c>
+      <c r="G19" t="str">
+        <v/>
+      </c>
+      <c r="H19" t="str">
+        <v/>
+      </c>
+      <c r="I19" t="str">
+        <v/>
+      </c>
+      <c r="J19" t="str">
+        <v/>
+      </c>
+      <c r="K19" t="str">
+        <v/>
+      </c>
+      <c r="L19" t="str">
         <v>seconds=180</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L18"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L19"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1394,4 +1433,327 @@
     <ignoredError numberStoredAsText="1" sqref="A1:Y5"/>
   </ignoredErrors>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:L8"/>
+  <cols>
+    <col min="1" max="1" width="5.83203125" customWidth="1"/>
+    <col min="2" max="2" width="18.83203125" customWidth="1"/>
+    <col min="3" max="3" width="35.83203125" customWidth="1"/>
+    <col min="4" max="4" width="35.83203125" customWidth="1"/>
+    <col min="5" max="5" width="35.83203125" customWidth="1"/>
+    <col min="6" max="6" width="35.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>id</v>
+      </c>
+      <c r="B1" t="str">
+        <v>type</v>
+      </c>
+      <c r="C1" t="str">
+        <v>ukr</v>
+      </c>
+      <c r="D1" t="str">
+        <v>rus</v>
+      </c>
+      <c r="E1" t="str">
+        <v>eng</v>
+      </c>
+      <c r="F1" t="str">
+        <v>ger</v>
+      </c>
+      <c r="G1" t="str">
+        <v>ukr_sub</v>
+      </c>
+      <c r="H1" t="str">
+        <v>rus_sub</v>
+      </c>
+      <c r="I1" t="str">
+        <v>eng_sub</v>
+      </c>
+      <c r="J1" t="str">
+        <v>ger_sub</v>
+      </c>
+      <c r="K1" t="str">
+        <v>href</v>
+      </c>
+      <c r="L1" t="str">
+        <v>meta</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="str">
+        <v>title</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Чеклист підготовки</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Чеклист подготовки</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Preparation checklist</v>
+      </c>
+      <c r="F2" t="str">
+        <v>Vorbereitungs-Checkliste</v>
+      </c>
+      <c r="G2" t="str">
+        <v/>
+      </c>
+      <c r="H2" t="str">
+        <v/>
+      </c>
+      <c r="I2" t="str">
+        <v/>
+      </c>
+      <c r="J2" t="str">
+        <v/>
+      </c>
+      <c r="K2" t="str">
+        <v/>
+      </c>
+      <c r="L2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="str">
+        <v>text</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Выполните эти пункты перед началом занятия.</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Выполните эти пункты перед началом занятия.</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Complete these steps before you start.</v>
+      </c>
+      <c r="F3" t="str">
+        <v>Führen Sie diese Schritte vor dem Start aus.</v>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v/>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="str">
+        <v>item</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Проверить оборудование</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Проверить оборудование</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Check the equipment</v>
+      </c>
+      <c r="F4" t="str">
+        <v>Geräte prüfen</v>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v/>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="str">
+        <v>item</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Подготовить рабочее место</v>
+      </c>
+      <c r="D5" t="str">
+        <v>Подготовить рабочее место</v>
+      </c>
+      <c r="E5" t="str">
+        <v>Prepare the workspace</v>
+      </c>
+      <c r="F5" t="str">
+        <v>Arbeitsplatz vorbereiten</v>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v/>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="str">
+        <v>item</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Прочитать технику выполнения</v>
+      </c>
+      <c r="D6" t="str">
+        <v>Прочитать технику выполнения</v>
+      </c>
+      <c r="E6" t="str">
+        <v>Read the procedure</v>
+      </c>
+      <c r="F6" t="str">
+        <v>Verfahren lesen</v>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v/>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="str">
+        <v>item</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Собрать необходимые материалы</v>
+      </c>
+      <c r="D7" t="str">
+        <v>Собрать необходимые материалы</v>
+      </c>
+      <c r="E7" t="str">
+        <v>Gather the required materials</v>
+      </c>
+      <c r="F7" t="str">
+        <v>Benötigte Materialien sammeln</v>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v/>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="str">
+        <v>item</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Проверить план урока</v>
+      </c>
+      <c r="D8" t="str">
+        <v>Проверить план урока</v>
+      </c>
+      <c r="E8" t="str">
+        <v>Review the lesson plan</v>
+      </c>
+      <c r="F8" t="str">
+        <v>Lehrplan überprüfen</v>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v/>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:L8"/>
+  </ignoredErrors>
+</worksheet>
 </file>